--- a/data/trans_bre/P2C_R1-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P2C_R1-Habitat-trans_bre.xlsx
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 0,94</t>
+          <t>-0,98; 0,93</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,37; 1,88</t>
+          <t>-0,44; 1,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,11; -0,18</t>
+          <t>-3,14; -0,13</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-10,44; 10,05</t>
+          <t>-8,26; 9,76</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,17 +685,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
+          <t>-97,36; —</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
           <t>—; —</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-100,0; 55,9</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-31,11; 49,32</t>
+          <t>-26,78; 51,29</t>
         </is>
       </c>
     </row>
@@ -760,27 +760,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-0,95; 1,63</t>
+          <t>-1,06; 1,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,85; 0,89</t>
+          <t>-0,86; 0,96</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,74; 1,17</t>
+          <t>-0,7; 1,2</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-7,05; 6,77</t>
+          <t>-5,7; 6,98</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-81,9; —</t>
+          <t>-78,06; 1004,3</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -790,12 +790,12 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-35,2; 64,36</t>
+          <t>-30,08; 68,78</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,2; 1,82</t>
+          <t>0,21; 1,85</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,67; 1,38</t>
+          <t>-1,51; 1,52</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,35; 2,01</t>
+          <t>-0,42; 2,08</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-24,93; -2,91</t>
+          <t>-26,33; -3,43</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,17 +885,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-91,81; 409,53</t>
+          <t>-83,1; 428,6</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-92,2; —</t>
+          <t>-79,99; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-95,26; -15,63</t>
+          <t>-94,29; -14,38</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,19; 0,9</t>
+          <t>-1,09; 0,89</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,73; 2,07</t>
+          <t>-0,7; 2,09</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,21; 1,52</t>
+          <t>-1,2; 1,43</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-2,93; 10,52</t>
+          <t>-3,09; 11,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-87,63; 308,75</t>
+          <t>-86,47; 335,78</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-55,35; 389,39</t>
+          <t>-49,53; 458,56</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-68,88; 348,99</t>
+          <t>-66,91; 250,87</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-17,32; 109,9</t>
+          <t>-17,17; 127,55</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 0,8</t>
+          <t>-0,39; 0,73</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,22; 0,97</t>
+          <t>-0,25; 1,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 0,64</t>
+          <t>-0,59; 0,59</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-11,92; 1,72</t>
+          <t>-11,4; 2,5</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-43,24; 243,11</t>
+          <t>-49,16; 212,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-28,56; 187,9</t>
+          <t>-28,45; 193,1</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-50,52; 101,51</t>
+          <t>-48,05; 98,26</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-63,94; 10,82</t>
+          <t>-58,91; 17,21</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2C_R1-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P2C_R1-Habitat-trans_bre.xlsx
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>0,68</t>
+          <t>1,44</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>5,75%</t>
         </is>
       </c>
     </row>
@@ -660,22 +660,22 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-0,98; 0,93</t>
+          <t>-0,98; 0,92</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-0,44; 1,99</t>
+          <t>-0,47; 1,92</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-3,14; -0,13</t>
+          <t>-3,1; -0,09</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-8,26; 9,76</t>
+          <t>-8,58; 10,29</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -685,17 +685,17 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-97,36; —</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>-100,0; 60,73</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-26,78; 51,29</t>
+          <t>-27,12; 52,69</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0,92</t>
+          <t>1,74</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>6,41%</t>
+          <t>13,54%</t>
         </is>
       </c>
     </row>
@@ -760,27 +760,27 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-1,06; 1,58</t>
+          <t>-0,92; 1,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-0,86; 0,96</t>
+          <t>-0,85; 0,94</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 1,2</t>
+          <t>-0,7; 1,24</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,7; 6,98</t>
+          <t>-5,16; 7,53</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-78,06; 1004,3</t>
+          <t>-82,64; —</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
@@ -795,7 +795,7 @@
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-30,08; 68,78</t>
+          <t>-28,47; 81,49</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>-11,0</t>
+          <t>-2,58</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>-71,9%</t>
+          <t>-18,53%</t>
         </is>
       </c>
     </row>
@@ -860,22 +860,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,21; 1,85</t>
+          <t>0,2; 1,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,51; 1,52</t>
+          <t>-1,55; 1,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-0,42; 2,08</t>
+          <t>-0,4; 2,16</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-26,33; -3,43</t>
+          <t>-11,43; 4,74</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -885,17 +885,17 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-83,1; 428,6</t>
+          <t>-88,45; 441,35</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-79,99; —</t>
+          <t>-83,15; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-94,29; -14,38</t>
+          <t>-57,35; 59,68</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4,51</t>
+          <t>4,77</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>34,74%</t>
+          <t>41,23%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-1,09; 0,89</t>
+          <t>-1,23; 1,0</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,7; 2,09</t>
+          <t>-0,98; 1,98</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-1,2; 1,43</t>
+          <t>-1,17; 1,52</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,09; 11,14</t>
+          <t>-1,11; 11,68</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-86,47; 335,78</t>
+          <t>-89,07; 346,07</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-49,53; 458,56</t>
+          <t>-55,79; 541,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-66,91; 250,87</t>
+          <t>-70,29; 315,16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-17,17; 127,55</t>
+          <t>-8,24; 151,38</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>-3,21</t>
+          <t>1,54</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>-19,32%</t>
+          <t>10,15%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-0,39; 0,73</t>
+          <t>-0,37; 0,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 1,0</t>
+          <t>-0,19; 1,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-0,59; 0,59</t>
+          <t>-0,6; 0,61</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-11,4; 2,5</t>
+          <t>-2,38; 4,7</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-49,16; 212,0</t>
+          <t>-45,44; 216,68</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-28,45; 193,1</t>
+          <t>-20,16; 185,9</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-48,05; 98,26</t>
+          <t>-47,68; 98,53</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-58,91; 17,21</t>
+          <t>-13,23; 37,08</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/P2C_R1-Habitat-trans_bre.xlsx
+++ b/data/trans_bre/P2C_R1-Habitat-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares con al menos un miembro que requiere cuidados y estos son remunerados</t>
+          <t>Población que convive con al menos un miembro que requiere cuidados y estos son remunerados</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
